--- a/KAMCHATKA_VERIFY_2010.xlsx
+++ b/KAMCHATKA_VERIFY_2010.xlsx
@@ -38662,12 +38662,13 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>+7 (351) 730-47-47 (пн-пт 8:30-17:30)</t>
+          <t>+7 (351) 730-47-47; +7 (922) 700-43-47
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>office@chsgs.ru; 166@ldtd.ru</t>
+          <t>office@chsgs.ru</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -38695,7 +38696,8 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 223-74-04</t>
+          <t>+7 (495) 223-74-04; 8-800-301-20-50
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -38728,7 +38730,8 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>8-800-444-74-74; +7 900 093-04-01</t>
+          <t>8-800-444-74-74; +7 (351) 246-02-10; +7 (351) 245-02-10
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -38761,7 +38764,8 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>+7 (749) 527-55-88 (как в каталоге productcenter — уточнить номер)</t>
+          <t>+7 (495) 275-58-88
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -38800,7 +38804,8 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>8 800 350-91-13</t>
+          <t>8-800-350-91-13
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -38833,7 +38838,8 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>8 800 444-00-28 (служба продаж); приёмная 8 800 222-15-44</t>
+          <t>8-800-444-00-28 (продажи); 8-800-222-15-44
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -38866,12 +38872,13 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 411-77-57 (Москва); Алексин +7 (48753) 2-70-25, 2-61-13 (по armtorg.ru)</t>
+          <t>+7 (495) 411-77-57
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>office@aztpa.ru; ngskr@aztpa.ru (клиновые задвижки)</t>
+          <t>office@ogscomp.ru (указан на aztpa.ru)</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -38899,7 +38906,8 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>+7 (34766) 2-99-10; отдел продаж (34766) 2-11-74, 2-13-57 (по ibprom.ru)</t>
+          <t>+7 (347) 662-99-10
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -38938,7 +38946,8 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83; Владивосток +7 (984) 159-21-64</t>
+          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83; Владивосток +7 (984) 159-21-64
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -38971,7 +38980,8 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>+7 (8412) 35-07-97; +7 (495) 668-10-92</t>
+          <t>+7 (495) 668-10-92; +7 (8412) 35-07-97; +7 (812) 309-54-81
+[сайт promarm.com, 22.10.2026]</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -39004,7 +39014,8 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>(49241) 2-32-41, 2-42-26, 8-920-925-81-95 (отдел сбыта, по armtorg.ru)</t>
+          <t>(49241) 2-32-41, 2-42-26, 8-920-925-81-95 (отдел сбыта, по armtorg.ru)
+[сайт armagus.ru не открылся 22.10 — номер из armtorg.ru, проверить звонком]</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -39037,12 +39048,13 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>+7 (351) 307-71-09</t>
+          <t>+7 (351) 307-71-09
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>info@zaoutk.ru</t>
+          <t>info@aoutk.ru</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -39076,7 +39088,8 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 792-57-57; 8-800-700-88-85</t>
+          <t>+7 (495) 792-57-57; 8-800-700-88-85
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -39109,7 +39122,8 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>8-800-201-58-67; +7 (48142) 2-88-09, 2-83-67</t>
+          <t>8-800-201-58-67; +7 (48142) 2-88-09, 2-83-67
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -39142,7 +39156,8 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>(49241) 2-32-41, 2-42-26</t>
+          <t>(49241) 2-32-41, 2-42-26
+[сайт armagus.ru не открылся 22.10 — номер из armtorg.ru, проверить звонком]</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -39175,12 +39190,13 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>уточнить на сайте</t>
+          <t>8-800-700-77-85; +7 (495) 792-11-05
+[сайт teplo-sila.com, 22.10.2026]</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>уточнить на сайте</t>
+          <t>marketing@teplo-sila.com</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -39214,7 +39230,8 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>8 800 350-91-13</t>
+          <t>8-800-350-91-13
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -39247,7 +39264,8 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>8 800 444-00-28</t>
+          <t>8-800-444-00-28 (продажи); 8-800-222-15-44
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -39280,7 +39298,8 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>+7 (812) 458-55-97; +7 (812) 334-92-39</t>
+          <t>+7 (812) 458-55-97; +7 (812) 334-92-39
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -39313,12 +39332,13 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 411-77-57</t>
+          <t>+7 (495) 411-77-57
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>office@aztpa.ru</t>
+          <t>office@ogscomp.ru (указан на aztpa.ru)</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -39352,7 +39372,8 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)</t>
+          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -39385,7 +39406,8 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>+7 (34766) 2-99-10</t>
+          <t>+7 (347) 662-99-10
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -39418,7 +39440,8 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>+7 (812) 458-55-97</t>
+          <t>+7 (812) 458-55-97
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -39451,7 +39474,8 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>через дилеров</t>
+          <t>через дилеров
+[только через дилеров (dn.ru)]</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -39490,7 +39514,8 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 792-57-57; 8-800-700-88-85</t>
+          <t>+7 (495) 792-57-57; 8-800-700-88-85
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -39523,7 +39548,8 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83</t>
+          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -39556,7 +39582,8 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>+7 (812) 458-55-97</t>
+          <t>+7 (812) 458-55-97
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -39589,7 +39616,8 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>(49241) 2-32-41, 2-42-26</t>
+          <t>(49241) 2-32-41, 2-42-26
+[сайт armagus.ru не открылся 22.10 — номер из armtorg.ru, проверить звонком]</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -39628,7 +39656,8 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)</t>
+          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -39661,12 +39690,13 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>уточнить на semlmz.ru</t>
+          <t>нет на сайте
+[semlmz.ru — контакты на сайте не опубликованы; не звонить, искать через дилеров]</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>уточнить на semlmz.ru</t>
+          <t>нет на сайте</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -39694,7 +39724,8 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>уточнить
+[не найден — не использовать]</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -39727,7 +39758,8 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>8 (495) 925-51-64</t>
+          <t>8 (495) 925-51-64
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -39766,7 +39798,8 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68</t>
+          <t>+7 (495) 937-89-68
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -39799,12 +39832,13 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>+7 (991) 210-60-21</t>
+          <t>8-800-200-52-76; +7 (991) 210-60-21
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>reklama@pik-algrupp.ru (общий)</t>
+          <t>sales@pik-algrupp.ru</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -39832,7 +39866,8 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>+7 (34766) 2-99-10</t>
+          <t>+7 (347) 662-99-10
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -39865,7 +39900,8 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>уточнить
+[не найден — не использовать]</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -39904,7 +39940,8 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>+7 (351) 730-47-47</t>
+          <t>+7 (351) 730-47-47; +7 (922) 700-43-47
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -39937,7 +39974,8 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68</t>
+          <t>+7 (495) 937-89-68
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -39970,7 +40008,8 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 223-74-04</t>
+          <t>+7 (495) 223-74-04; 8-800-301-20-50
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -40003,7 +40042,8 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>через дилеров</t>
+          <t>через дилеров
+[только через дилеров (dn.ru)]</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -40042,7 +40082,8 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>+7 (499) 653-65-06</t>
+          <t>+7 (499) 653-65-06
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -40075,7 +40116,8 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>(8453) 75-48-28, 75-48-82</t>
+          <t>(8453) 75-48-28, 75-48-82
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -40108,7 +40150,8 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>уточнить
+[консультация, не поставщик]</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -40147,7 +40190,8 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>+7 (4872) 72-47-16 (отдел реализации)</t>
+          <t>+7 (4872) 72-47-16 (отдел реализации)
+[сайт tulaprivod.ru не открылся 22.10 — проверить звонком]</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -40180,7 +40224,8 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>(8352) 305-148, 305-221</t>
+          <t>+7 (8352) 30-51-48; 30-52-21; Москва +7 (495) 735-42-44
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -40213,7 +40258,8 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>(49241) 2-32-41</t>
+          <t>(49241) 2-32-41
+[сайт armagus.ru не открылся 22.10 — номер из armtorg.ru, проверить звонком]</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -40252,7 +40298,8 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>+7 (351) 730-47-47</t>
+          <t>+7 (351) 730-47-47; +7 (922) 700-43-47
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -40285,7 +40332,8 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>+7 (812) 458-55-97</t>
+          <t>+7 (812) 458-55-97
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -40318,7 +40366,8 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>+7 (812) 611-03-77; 8-800-775-74-84</t>
+          <t>+7 (812) 611-03-77; 8-800-775-74-84
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -40357,12 +40406,13 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>+7 (812) 325-90-51; +7 (495) 666-33-01</t>
+          <t>+7 (812) 325-90-51; +7 (495) 666-33-01
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>info@rosma.spb.ru (уточнить)</t>
+          <t>info@rosma.spb.ru</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -40390,7 +40440,8 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>+7 (812) 611-03-77</t>
+          <t>+7 (812) 611-03-77
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -40423,7 +40474,8 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>через дилеров</t>
+          <t>через дилеров
+[только через дилеров (dn.ru)]</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
